--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486771_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486771_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.5909</v>
+        <v>8.7966</v>
       </c>
       <c r="E2" t="n">
-        <v>9.4391</v>
+        <v>8.8186</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1518</v>
+        <v>-0.022</v>
       </c>
       <c r="G2" t="n">
         <v>6.6601</v>
@@ -610,13 +610,13 @@
         <v>1.3515</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2012</v>
+        <v>1.4068</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2959</v>
+        <v>0.6754</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9053</v>
+        <v>0.7315</v>
       </c>
       <c r="V2" t="n">
         <v>-0.0426</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.5941</v>
+        <v>5.7913</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9128</v>
+        <v>3.5885</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6813</v>
+        <v>2.2028</v>
       </c>
       <c r="G3" t="n">
         <v>4.4808</v>
@@ -688,13 +688,13 @@
         <v>1.5446</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.149</v>
+        <v>1.0482</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1383</v>
+        <v>0.5375</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0107</v>
+        <v>0.5107</v>
       </c>
       <c r="V3" t="n">
         <v>1.2277</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.0188</v>
+        <v>4.3206</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7594</v>
+        <v>3.4833</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2594</v>
+        <v>0.8372000000000001</v>
       </c>
       <c r="G4" t="n">
         <v>2.0336</v>
@@ -766,13 +766,13 @@
         <v>1.7377</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4638</v>
+        <v>0.7655999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8277</v>
+        <v>-0.1038</v>
       </c>
       <c r="U4" t="n">
-        <v>1.2916</v>
+        <v>0.8694</v>
       </c>
       <c r="V4" t="n">
         <v>0.9421</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.7244</v>
+        <v>4.1106</v>
       </c>
       <c r="E5" t="n">
-        <v>3.374</v>
+        <v>3.636</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3504</v>
+        <v>0.4745</v>
       </c>
       <c r="G5" t="n">
         <v>3.6139</v>
@@ -844,13 +844,13 @@
         <v>1.3515</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1104</v>
+        <v>0.4966</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3038</v>
+        <v>-0.0418</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4142</v>
+        <v>0.5384</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. CAULIN TORNERO</t>
+          <t>D. DAMIAN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.3859</v>
+        <v>1.0733</v>
       </c>
       <c r="E6" t="n">
-        <v>3.2913</v>
+        <v>0.026</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9054</v>
+        <v>1.0472</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6019</v>
+        <v>2.5624</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9863</v>
+        <v>0.8556</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.3843</v>
+        <v>1.7068</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0576</v>
+        <v>3.019</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3658</v>
+        <v>1.0635</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6918</v>
+        <v>1.9555</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4557</v>
+        <v>-0.4566</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6205000000000001</v>
+        <v>-0.2079</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.0761</v>
+        <v>-0.2487</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1931</v>
+        <v>-2.1239</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1931</v>
+        <v>-3.2823</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3862</v>
+        <v>1.1585</v>
       </c>
       <c r="S6" t="n">
-        <v>2.1621</v>
+        <v>0.6347</v>
       </c>
       <c r="T6" t="n">
-        <v>2.4268</v>
+        <v>0.2893</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2647</v>
+        <v>0.3454</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5712</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5712</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. DAMIAN</t>
+          <t>A. CAULIN TORNERO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1892</v>
+        <v>1.0098</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1808</v>
+        <v>1.6918</v>
       </c>
       <c r="F7" t="n">
-        <v>1.3701</v>
+        <v>-0.6819</v>
       </c>
       <c r="G7" t="n">
-        <v>2.5624</v>
+        <v>0.6019</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8556</v>
+        <v>0.9863</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7068</v>
+        <v>-0.3843</v>
       </c>
       <c r="J7" t="n">
-        <v>3.019</v>
+        <v>1.0576</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0635</v>
+        <v>0.3658</v>
       </c>
       <c r="L7" t="n">
-        <v>1.9555</v>
+        <v>0.6918</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4566</v>
+        <v>-0.4557</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2079</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2487</v>
+        <v>-1.0761</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.1239</v>
+        <v>0.1931</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.2823</v>
+        <v>-0.1931</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1585</v>
+        <v>0.3862</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7507</v>
+        <v>0.786</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0825</v>
+        <v>0.8273</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6682</v>
+        <v>-0.0412</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.5712</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4399</v>
+        <v>-0.1834</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3212</v>
+        <v>-0.1143</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1188</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="G8" t="n">
         <v>-0.3627</v>
@@ -1078,13 +1078,13 @@
         <v>0.1931</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.07729999999999999</v>
+        <v>0.1793</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1104</v>
+        <v>0.0965</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0331</v>
+        <v>0.0828</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9297</v>
+        <v>-0.7518</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1861</v>
+        <v>-1.0827</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2564</v>
+        <v>0.3309</v>
       </c>
       <c r="G9" t="n">
         <v>0.2068</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1711</v>
+        <v>0.0069</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2207</v>
+        <v>-0.1173</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0497</v>
+        <v>0.1242</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.756</v>
+        <v>-1.312</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5527</v>
+        <v>-0.0838</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2033</v>
+        <v>-1.2281</v>
       </c>
       <c r="G10" t="n">
         <v>0.5087</v>
@@ -1234,13 +1234,13 @@
         <v>0.5792</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4578</v>
+        <v>-0.0137</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4415</v>
+        <v>0.0274</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0163</v>
+        <v>-0.0411</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2277</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.4517</v>
+        <v>-5.653</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.4083</v>
+        <v>-3.56</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.0434</v>
+        <v>-2.093</v>
       </c>
       <c r="G11" t="n">
         <v>-2.8226</v>
@@ -1312,13 +1312,13 @@
         <v>0.3862</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2703</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3032</v>
+        <v>0.1515</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0329</v>
+        <v>-0.0825</v>
       </c>
       <c r="V11" t="n">
         <v>-2.1271</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>16.926</v>
+        <v>17.202</v>
       </c>
       <c r="E12" t="n">
-        <v>16.1275</v>
+        <v>16.4034</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7984999999999993</v>
+        <v>0.7985000000000002</v>
       </c>
       <c r="G12" t="n">
         <v>17.4829</v>
@@ -1390,13 +1390,13 @@
         <v>8.688499999999999</v>
       </c>
       <c r="S12" t="n">
-        <v>5.103300000000001</v>
+        <v>5.3794</v>
       </c>
       <c r="T12" t="n">
-        <v>2.066</v>
+        <v>2.342</v>
       </c>
       <c r="U12" t="n">
-        <v>3.0375</v>
+        <v>3.0376</v>
       </c>
       <c r="V12" t="n">
         <v>-1.7988</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.6582</v>
+        <v>3.5092</v>
       </c>
       <c r="E13" t="n">
         <v>3.2343</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4239</v>
+        <v>0.2749</v>
       </c>
       <c r="G13" t="n">
         <v>1.8473</v>
@@ -1468,13 +1468,13 @@
         <v>1.5446</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3476</v>
+        <v>-0.4966</v>
       </c>
       <c r="T13" t="n">
         <v>-0.3039</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0437</v>
+        <v>-0.1927</v>
       </c>
       <c r="V13" t="n">
         <v>0.6138</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.7089</v>
+        <v>0.6344</v>
       </c>
       <c r="E14" t="n">
         <v>0.6277</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0813</v>
+        <v>0.0068</v>
       </c>
       <c r="G14" t="n">
         <v>0.6206</v>
@@ -1546,13 +1546,13 @@
         <v>0.1931</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1047</v>
+        <v>-0.1792</v>
       </c>
       <c r="T14" t="n">
         <v>-0.0552</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0495</v>
+        <v>-0.124</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,10 +1579,10 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2008</v>
+        <v>0.4076</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6841</v>
+        <v>0.8909</v>
       </c>
       <c r="F15" t="n">
         <v>-0.4833</v>
@@ -1624,10 +1624,10 @@
         <v>1.1585</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4138</v>
+        <v>-0.207</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.276</v>
+        <v>-0.0692</v>
       </c>
       <c r="U15" t="n">
         <v>-0.1378</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.8318</v>
+        <v>-0.6084000000000001</v>
       </c>
       <c r="E16" t="n">
         <v>-0.6833</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1486</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="G16" t="n">
         <v>-0.4565</v>
@@ -1702,13 +1702,13 @@
         <v>1.3515</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7615</v>
+        <v>-0.538</v>
       </c>
       <c r="T16" t="n">
         <v>-0.1384</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6231</v>
+        <v>-0.3996</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.909</v>
+        <v>-1.1655</v>
       </c>
       <c r="E17" t="n">
-        <v>1.1529</v>
+        <v>0.9461000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.0619</v>
+        <v>-2.1116</v>
       </c>
       <c r="G17" t="n">
         <v>-3.6027</v>
@@ -1780,13 +1780,13 @@
         <v>1.7377</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5573</v>
+        <v>-0.8138</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4418</v>
+        <v>-0.6487000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1155</v>
+        <v>-0.1651</v>
       </c>
       <c r="V17" t="n">
         <v>1.5133</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.5474</v>
+        <v>-2.655</v>
       </c>
       <c r="E18" t="n">
-        <v>2.308</v>
+        <v>2.1012</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.8554</v>
+        <v>-4.7561</v>
       </c>
       <c r="G18" t="n">
         <v>0.0939</v>
@@ -1858,13 +1858,13 @@
         <v>1.9308</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7339</v>
+        <v>-0.8414</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3039</v>
+        <v>-0.5108</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4299</v>
+        <v>-0.3306</v>
       </c>
       <c r="V18" t="n">
         <v>-0.9421</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.4599</v>
+        <v>-4.7205</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3169</v>
+        <v>-0.6271</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.143</v>
+        <v>-4.0934</v>
       </c>
       <c r="G19" t="n">
         <v>-3.0445</v>
@@ -1936,13 +1936,13 @@
         <v>0.9654</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1877</v>
+        <v>-0.4483</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1927</v>
+        <v>-0.1175</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3805</v>
+        <v>-0.3308</v>
       </c>
       <c r="V19" t="n">
         <v>-1.2277</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. RODRIGUEZ HERNANDEZ</t>
+          <t>E. GONZALEZ CAMEJO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-6.1145</v>
+        <v>-6.0892</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.6557</v>
+        <v>-2.6324</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.4588</v>
+        <v>-3.4568</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.8982</v>
+        <v>-8.499000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.8138</v>
+        <v>-7.2194</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.0844</v>
+        <v>-1.2796</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.1801</v>
+        <v>-3.7937</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.572</v>
+        <v>-3.839</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6081</v>
+        <v>0.0453</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.7181</v>
+        <v>-4.7052</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.2418</v>
+        <v>-3.3804</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.4763</v>
+        <v>-1.3248</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.5446</v>
+        <v>1.3515</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.8962</v>
+        <v>-0.9654</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3515</v>
+        <v>2.3169</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3861</v>
+        <v>-1.069</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5795</v>
+        <v>-0.6143</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1934</v>
+        <v>-0.4547</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.2856</v>
+        <v>2.1271</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.741</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2856</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. GONZALEZ CAMEJO</t>
+          <t>S. RODRIGUEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.6312</v>
+        <v>-6.2387</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.1495</v>
+        <v>-4.6557</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.4816</v>
+        <v>-1.583</v>
       </c>
       <c r="G21" t="n">
-        <v>-8.499000000000001</v>
+        <v>-3.8982</v>
       </c>
       <c r="H21" t="n">
-        <v>-7.2194</v>
+        <v>-1.8138</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.2796</v>
+        <v>-2.0844</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.7937</v>
+        <v>-1.1801</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.839</v>
+        <v>-0.572</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0453</v>
+        <v>-0.6081</v>
       </c>
       <c r="M21" t="n">
-        <v>-4.7052</v>
+        <v>-2.7181</v>
       </c>
       <c r="N21" t="n">
-        <v>-3.3804</v>
+        <v>-1.2418</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.3248</v>
+        <v>-1.4763</v>
       </c>
       <c r="P21" t="n">
+        <v>-1.5446</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-2.8962</v>
+      </c>
+      <c r="R21" t="n">
         <v>1.3515</v>
       </c>
-      <c r="Q21" t="n">
-        <v>-0.9654</v>
-      </c>
-      <c r="R21" t="n">
-        <v>2.3169</v>
-      </c>
       <c r="S21" t="n">
-        <v>-1.6109</v>
+        <v>-0.5103</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.1314</v>
+        <v>-0.5795</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4795</v>
+        <v>0.0692</v>
       </c>
       <c r="V21" t="n">
-        <v>2.1271</v>
+        <v>-0.2856</v>
       </c>
       <c r="W21" t="n">
-        <v>2.741</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6138</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-16.9259</v>
+        <v>-16.9261</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.7984000000000013</v>
+        <v>-0.7983000000000002</v>
       </c>
       <c r="F22" t="n">
-        <v>-16.1274</v>
+        <v>-16.1276</v>
       </c>
       <c r="G22" t="n">
         <v>-17.483</v>
@@ -2158,7 +2158,7 @@
         <v>-16.2124</v>
       </c>
       <c r="O22" t="n">
-        <v>-5.2452</v>
+        <v>-5.245200000000001</v>
       </c>
       <c r="P22" t="n">
         <v>3.8616</v>
@@ -2170,10 +2170,10 @@
         <v>12.55</v>
       </c>
       <c r="S22" t="n">
-        <v>-5.1035</v>
+        <v>-5.103599999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-3.0374</v>
+        <v>-3.0375</v>
       </c>
       <c r="U22" t="n">
         <v>-2.0661</v>
@@ -2185,7 +2185,7 @@
         <v>6.9526</v>
       </c>
       <c r="X22" t="n">
-        <v>-5.153700000000001</v>
+        <v>-5.1537</v>
       </c>
     </row>
   </sheetData>
